--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104627_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104627_W19.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7405</v>
+        <v>7.1618</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5472</v>
+        <v>5.7545</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1933</v>
+        <v>1.4073</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3189</v>
+        <v>5.3139</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0115</v>
+        <v>1.0137</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3074</v>
+        <v>4.3002</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6038</v>
+        <v>4.5805</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9529</v>
+        <v>3.9394</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7151</v>
+        <v>0.7335</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9394</v>
+        <v>-0.5179</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7174</v>
+        <v>2.6987</v>
       </c>
       <c r="E3" t="n">
-        <v>2.621</v>
+        <v>2.6103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0964</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8672</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.068</v>
+        <v>-1.0575</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9352</v>
+        <v>1.935</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0202</v>
+        <v>2.01</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.153</v>
+        <v>-1.1325</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0572</v>
+        <v>-0.0893</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0544</v>
+        <v>0.0556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7034</v>
+        <v>2.6663</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8696</v>
+        <v>0.7004</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1662</v>
+        <v>1.9659</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3844</v>
+        <v>1.9021</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1282</v>
+        <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2562</v>
+        <v>1.7335</v>
       </c>
       <c r="J4" t="n">
-        <v>6.9133</v>
+        <v>2.1015</v>
       </c>
       <c r="K4" t="n">
-        <v>1.697</v>
+        <v>0.6722</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2162</v>
+        <v>1.4292</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5289</v>
+        <v>-0.1993</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5689</v>
+        <v>-0.5036</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.722</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1337</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.493</v>
+        <v>-0.4207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3593</v>
+        <v>-0.1111</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2946</v>
+        <v>2.4681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6108</v>
+        <v>2.3496</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6838</v>
+        <v>0.1184</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8973</v>
+        <v>6.3774</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1542</v>
+        <v>1.1423</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7432</v>
+        <v>5.2351</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1226</v>
+        <v>6.8794</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6754</v>
+        <v>1.6892</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4472</v>
+        <v>5.1902</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2252</v>
+        <v>-0.502</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5212</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2959</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.0882</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5383</v>
+        <v>0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3593</v>
+        <v>-0.1111</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5724</v>
+        <v>1.7265</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0701</v>
+        <v>-1.1114</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6424</v>
+        <v>2.8379</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7037</v>
+        <v>1.8414</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8889</v>
+        <v>-0.2618</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8148</v>
+        <v>2.1032</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5508</v>
+        <v>0.8354</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7175</v>
+        <v>-0.907</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8334</v>
+        <v>1.7425</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1529</v>
+        <v>1.006</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1715</v>
+        <v>0.6452</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0186</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3865</v>
+        <v>-0.7978</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6079</v>
+        <v>-0.8087</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9944</v>
+        <v>0.0108</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4005</v>
+        <v>1.2239</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4069</v>
+        <v>0.1155</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8075</v>
+        <v>1.1084</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3656</v>
+        <v>4.6923</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4646</v>
+        <v>1.8816</v>
       </c>
       <c r="I7" t="n">
-        <v>0.901</v>
+        <v>2.8107</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4494</v>
+        <v>4.5181</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0016</v>
+        <v>1.6957</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4478</v>
+        <v>2.8223</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0839</v>
+        <v>0.1743</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5371</v>
+        <v>0.1859</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4532</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2683</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5367</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4355</v>
+        <v>0.0582</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2662</v>
+        <v>-0.3719</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1693</v>
+        <v>0.4302</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8678</v>
+        <v>-1.7057</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4141</v>
+        <v>-0.6162</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.204</v>
+        <v>1.0418</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3238</v>
+        <v>-0.8016</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5277</v>
+        <v>1.8434</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8358</v>
+        <v>2.3765</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.27</v>
+        <v>1.4675</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1057</v>
+        <v>0.909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8538</v>
+        <v>2.4323</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8974</v>
+        <v>1.9855</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7512</v>
+        <v>0.4468</v>
       </c>
       <c r="M8" t="n">
-        <v>0.982</v>
+        <v>-0.0558</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6274</v>
+        <v>-0.518</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3546</v>
+        <v>0.4622</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3123</v>
+        <v>0.0814</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0434</v>
+        <v>-0.0863</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2689</v>
+        <v>0.1677</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2836</v>
+        <v>0.1689</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0165</v>
+        <v>0.007</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2671</v>
+        <v>0.1619</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1335</v>
+        <v>0.1373</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4934</v>
+        <v>0.4994</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3599</v>
+        <v>-0.3621</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4339</v>
+        <v>0.4252</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1083</v>
+        <v>1.1032</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0502</v>
+        <v>-0.1765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3672</v>
+        <v>0.2418</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0594</v>
+        <v>0.1502</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6094</v>
+        <v>1.5969</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6688</v>
+        <v>-1.4467</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9361</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0561</v>
+        <v>1.0678</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.12</v>
+        <v>-0.1207</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8978</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0383</v>
+        <v>0.0584</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6248</v>
+        <v>-0.4389</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3811</v>
+        <v>-0.3812</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1806</v>
+        <v>-0.4341</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0593</v>
+        <v>-1.0932</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8787</v>
+        <v>0.6591</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4643</v>
+        <v>-1.4667</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0921</v>
+        <v>1.105</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5564</v>
+        <v>-2.5718</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1135</v>
+        <v>-1.1383</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3507</v>
+        <v>-0.3284</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0569</v>
+        <v>-0.195</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4506</v>
+        <v>-0.4509</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5075</v>
+        <v>0.2559</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0449</v>
+        <v>-4.2451</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4859</v>
+        <v>-4.5088</v>
       </c>
       <c r="F12" t="n">
-        <v>0.441</v>
+        <v>0.2638</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4358</v>
+        <v>0.4365</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1022</v>
+        <v>0.095</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1808</v>
+        <v>-0.1708</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1101</v>
+        <v>-0.2995</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0587</v>
+        <v>-0.2483</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.6315</v>
+        <v>14.627</v>
       </c>
       <c r="E13" t="n">
-        <v>5.928500000000001</v>
+        <v>5.619200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>8.7029</v>
+        <v>9.007800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>22.8995</v>
+        <v>22.923</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3868</v>
+        <v>7.4632</v>
       </c>
       <c r="I13" t="n">
-        <v>15.5128</v>
+        <v>15.4598</v>
       </c>
       <c r="J13" t="n">
-        <v>23.8343</v>
+        <v>23.6277</v>
       </c>
       <c r="K13" t="n">
-        <v>8.4283</v>
+        <v>8.334200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>15.4058</v>
+        <v>15.2933</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9345000000000002</v>
+        <v>-0.7045000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0418</v>
+        <v>-0.8710000000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1071</v>
+        <v>0.1667000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.4152</v>
+        <v>-20.4869</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1467</v>
+        <v>18.2107</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9791</v>
+        <v>-2.9953</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.372100000000001</v>
+        <v>-3.3707</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3929999999999999</v>
+        <v>0.3754000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.0209</v>
+        <v>-3.0244</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8813</v>
+        <v>5.8492</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.902200000000001</v>
+        <v>-8.873599999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2484</v>
+        <v>6.9864</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1638</v>
+        <v>6.2328</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.7536</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2079</v>
+        <v>-3.1989</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2626</v>
+        <v>0.2641</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4705</v>
+        <v>-3.463</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1282</v>
+        <v>0.1084</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0665</v>
+        <v>1.0547</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3361</v>
+        <v>-3.3073</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0979</v>
+        <v>-0.3531</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0253</v>
+        <v>-0.9086</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0726</v>
+        <v>0.5554</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9663</v>
+        <v>8.945</v>
       </c>
       <c r="W14" t="n">
-        <v>8.195</v>
+        <v>8.171099999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7129</v>
+        <v>1.9876</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4368</v>
+        <v>0.651</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2761</v>
+        <v>1.3366</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0791</v>
+        <v>-2.0784</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1138</v>
+        <v>-2.122</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0347</v>
+        <v>0.0436</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7579</v>
+        <v>-0.7748</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8698</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3212</v>
+        <v>-1.3036</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.244</v>
+        <v>-1.2355</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0453</v>
+        <v>1.3133</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3288</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7165</v>
+        <v>0.7493</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1796</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0522</v>
+        <v>0.3029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2318</v>
+        <v>0.4234</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1587</v>
+        <v>0.1607</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.206</v>
+        <v>0.3379</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>0.2856</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1364</v>
+        <v>0.0523</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0612</v>
+        <v>-0.3879</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8262</v>
+        <v>0.0373</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8874</v>
+        <v>-0.4252</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1015</v>
+        <v>-1.7616</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4546</v>
+        <v>1.5229</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5561</v>
+        <v>-3.2845</v>
       </c>
       <c r="J17" t="n">
+        <v>1.7589</v>
+      </c>
+      <c r="K17" t="n">
         <v>1.7819</v>
       </c>
-      <c r="K17" t="n">
-        <v>1.7073</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>-0.023</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8834</v>
+        <v>-3.5205</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2526</v>
+        <v>-0.259</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.6308</v>
+        <v>-3.2615</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0668</v>
+        <v>0.2356</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1785</v>
+        <v>-0.5835</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1116</v>
+        <v>0.819</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3334</v>
+        <v>-0.7241</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2758</v>
+        <v>0.6912</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0576</v>
+        <v>-1.4153</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7511</v>
+        <v>-1.0958</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5355</v>
+        <v>1.4479</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2866</v>
+        <v>-2.5437</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7959</v>
+        <v>1.7669</v>
       </c>
       <c r="K18" t="n">
-        <v>1.804</v>
+        <v>1.6925</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0081</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.547</v>
+        <v>-2.8628</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2685</v>
+        <v>-0.2446</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.2785</v>
+        <v>-2.6182</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7165</v>
+        <v>0.3913</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9376</v>
+        <v>0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2211</v>
+        <v>0.3289</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1326</v>
+        <v>-2.0681</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9679</v>
+        <v>-2.1744</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1647</v>
+        <v>0.1063</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.7277</v>
+        <v>-1.1192</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0702</v>
+        <v>-1.0999</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6575</v>
+        <v>-0.0193</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9539</v>
+        <v>-0.7179</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6126</v>
+        <v>-0.7552</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3413</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7738</v>
+        <v>-0.4012</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4576</v>
+        <v>-0.3447</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3162</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4875</v>
+        <v>-0.0384</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1202</v>
+        <v>-0.0907</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3673</v>
+        <v>0.0523</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2145</v>
+        <v>-2.2921</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2841</v>
+        <v>-1.71</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0696</v>
+        <v>-0.582</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1194</v>
+        <v>-3.6036</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0981</v>
+        <v>-2.0563</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0213</v>
+        <v>-1.5473</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7144</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7517</v>
+        <v>-0.6485</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.405</v>
+        <v>-3.0668</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3463</v>
+        <v>-1.4078</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0586</v>
+        <v>-1.659</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1878</v>
+        <v>0.6271</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>0.1925</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>0.4345</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.555</v>
+        <v>-2.3451</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8491</v>
+        <v>-1.7481</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7058</v>
+        <v>-0.597</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6558</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0426</v>
+        <v>-0.0385</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1541</v>
+        <v>0.1467</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8099</v>
+        <v>-0.8025</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3548</v>
+        <v>-0.1429</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8354</v>
+        <v>-3.735</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2859</v>
+        <v>-3.4274</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5495</v>
+        <v>-0.3076</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6113</v>
+        <v>-5.7476</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0547</v>
+        <v>-3.0948</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5566</v>
+        <v>-2.6528</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-2.9994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-2.6489</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>-0.3505</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0857</v>
+        <v>-2.7481</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4171</v>
+        <v>-0.4458</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6685</v>
+        <v>-2.3023</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0974</v>
+        <v>1.894</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4966</v>
+        <v>1.1839</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2249</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2249</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7594</v>
+        <v>-4.5356</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2536</v>
+        <v>-3.3635</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5058</v>
+        <v>-1.1721</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2618</v>
+        <v>-3.2717</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.287</v>
+        <v>-0.2954</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9747</v>
+        <v>-2.9763</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2952</v>
+        <v>0.2513</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0523</v>
+        <v>1.0267</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5569</v>
+        <v>-3.523</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.405</v>
+        <v>0.8256</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1462</v>
+        <v>-0.2003</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7413</v>
+        <v>1.0259</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8807</v>
+        <v>-5.8707</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0005</v>
+        <v>-4.3417</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8802</v>
+        <v>-1.529</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5512</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4038</v>
+        <v>-1.4153</v>
       </c>
       <c r="I24" t="n">
-        <v>0.861</v>
+        <v>0.8641</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7138</v>
+        <v>1.6839</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5273</v>
+        <v>1.519</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2566</v>
+        <v>-2.2351</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5903</v>
+        <v>-1.5802</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7501</v>
+        <v>0.2739</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8166</v>
+        <v>-0.1072</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0665</v>
+        <v>0.3812</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.6313</v>
+        <v>-12.2583</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.542299999999999</v>
+        <v>-8.849900000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.088900000000001</v>
+        <v>-3.408299999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-22.8997</v>
+        <v>-22.9231</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.386699999999999</v>
+        <v>-7.4633</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.5129</v>
+        <v>-15.4598</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9345000000000004</v>
+        <v>0.7043999999999997</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0417</v>
+        <v>0.8709</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1071</v>
+        <v>-0.1666000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-23.8342</v>
+        <v>-23.6274</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.4282</v>
+        <v>-8.334200000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-15.4057</v>
+        <v>-15.2933</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2684</v>
+        <v>2.2764</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1467</v>
+        <v>-18.2107</v>
       </c>
       <c r="R25" t="n">
-        <v>20.4151</v>
+        <v>20.4869</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9789</v>
+        <v>5.3643</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3931</v>
+        <v>-0.3754</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3722</v>
+        <v>5.7395</v>
       </c>
       <c r="V25" t="n">
-        <v>3.0208</v>
+        <v>3.0244</v>
       </c>
       <c r="W25" t="n">
-        <v>9.062800000000001</v>
+        <v>9.031399999999998</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.0421</v>
+        <v>-6.007</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104627_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104627_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.873599999999998</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104627_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.007</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
